--- a/docs/snapshot/downloads/privacy.xlsx
+++ b/docs/snapshot/downloads/privacy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SKT  휴대폰 본인확인서비스 중단 공지(7.12 01:00 ~ 04:00)</t>
+          <t>개인정보 포털 예방점검에 따른 서비스 중단 안내 (8.13 19:00 ~ 23:00)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,39 +476,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20908</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20909</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-09 10:02:18.348370+09:00</t>
+          <t>2026-08-10 18:01:43.365104+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-09 10:02:18.348370+09:00</t>
+          <t>2026-08-10 18:01:43.365104+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 전문교육(하반기) 안내</t>
+          <t>SKT  휴대폰 본인확인서비스 중단 공지(7.12 01:00 ~ 04:00)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -518,39 +518,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20907</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20908</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
+          <t>2026-07-09 10:02:18.348370+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
+          <t>2026-07-09 10:02:18.348370+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인확인 내역조회, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.6.16 (화) 19:00 ~20:00)</t>
+          <t>2026년 개인정보 영향평가 전문교육(하반기) 안내</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20906</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20907</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -587,12 +587,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>정보주체 권리행사(본인확인 내역조회, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.6.16 (화) 19:00 ~20:00)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20903</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20906</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -629,12 +629,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>개인정보 포털 DB점검에 따른 서비스 중단 안내 (5.26 19:00 ~ 21:00)</t>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20900</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20903</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -671,12 +671,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(복구완료) 외국인 실명확인 서비스 장애 안내(26.05.19 13:47 ~18:50 )</t>
+          <t>개인정보 포털 DB점검에 따른 서비스 중단 안내 (5.26 19:00 ~ 21:00)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20896</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20900</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>제3기 가명정보 전문가 풀 모집 공고</t>
+          <t>(복구완료) 외국인 실명확인 서비스 장애 안내(26.05.19 13:47 ~18:50 )</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20895</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20895</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20896</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SKT 휴대폰 본인확인서비스 중단 공지(5.10 03:20 ~ 03:25 / 5.12 03:20 ~ 03:25)</t>
+          <t>제3기 가명정보 전문가 풀 모집 공고</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -770,17 +770,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20894</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20895</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -797,12 +797,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 인증시험(1차) 안내</t>
+          <t>SKT 휴대폰 본인확인서비스 중단 공지(5.10 03:20 ~ 03:25 / 5.12 03:20 ~ 03:25)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20893</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20894</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>본인인증 서비스 장애 발생 공지(2026.04.28(화)15:00 ~ 15:10)</t>
+          <t>2026년 개인정보 영향평가 인증시험(1차) 안내</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20888</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20893</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -881,12 +881,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>개인정보 영향평가 전문인력 인증서 발급 및 유효기간 관련 안내</t>
+          <t>본인인증 서비스 장애 발생 공지(2026.04.28(화)15:00 ~ 15:10)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20884</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20888</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -923,12 +923,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 계속교육 일정 안내</t>
+          <t>개인정보 영향평가 전문인력 인증서 발급 및 유효기간 관련 안내</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20878</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20884</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.4.8 (수) 03:00 ~05:00)</t>
+          <t>2026년 개인정보 영향평가 계속교육 일정 안내</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20875</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20878</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내 (2026년 3월 24일(화) 23:00~ 3월 25일(수) 02:00)</t>
+          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.4.8 (수) 03:00 ~05:00)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20874</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20875</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1049,12 +1049,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.03.24(화)22:00 ~ 2026.03.25(수) 02:00)</t>
+          <t>본인확인 서비스 작업 공지 안내 (2026년 3월 24일(화) 23:00~ 3월 25일(수) 02:00)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20873</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20874</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1091,12 +1091,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 전문교육(상반기) 안내</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.03.24(화)22:00 ~ 2026.03.25(수) 02:00)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20872</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20872</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20873</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>외국인 실명확인 서비스 작업 공지 안내</t>
+          <t>2026년 개인정보 영향평가 전문교육(상반기) 안내</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20871</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20872</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.03.24. (화) 02:00 ~ 04:00)</t>
+          <t>외국인 실명확인 서비스 작업 공지 안내</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20870</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20871</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1217,12 +1217,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.01.22 (목) 22:00 ~2026.01.23 (금) 05:00)</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.03.24. (화) 02:00 ~ 04:00)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20868</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20870</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.01.21 (수) 19:00 ~21:00)</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.01.22 (목) 22:00 ~2026.01.23 (금) 05:00)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20867</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20868</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1301,12 +1301,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>개인정보 포털 사용자 편의성 설문조사 참여 이벤트 당첨자 발표</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.01.21 (수) 19:00 ~21:00)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20866</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20867</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1343,12 +1343,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 보호·활용 분야 R&amp;amp;D 사업 신규지원 대상과제 공고(~2.10. 오후 3시)</t>
+          <t>개인정보 포털 사용자 편의성 설문조사 참여 이벤트 당첨자 발표</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1358,17 +1358,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20865</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20866</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1385,12 +1385,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.1.12 (월) 05:00 ~06:00)</t>
+          <t>2026년도 개인정보 보호·활용 분야 R&amp;amp;D 사업 신규지원 대상과제 공고(~2.10. 오후 3시)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1400,17 +1400,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20862</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20865</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1427,12 +1427,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>「개인정보관리 전문기관 지정 심사위원회」 심사위원 모집 안내 (~12.23. 18시까지)</t>
+          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.1.12 (월) 05:00 ~06:00)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20856</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20862</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1469,12 +1469,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>외국인 본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.17 (수) 16:00 ~17:00)</t>
+          <t>「개인정보관리 전문기관 지정 심사위원회」 심사위원 모집 안내 (~12.23. 18시까지)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20855</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20856</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.15 (월) 08:00 ~09:00)</t>
+          <t>외국인 본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.17 (수) 16:00 ~17:00)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20854</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20855</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1553,40 +1553,82 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.15 (월) 08:00 ~09:00)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20854</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20854</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2025년 개인정보 영향평가 인증시험(2차) 안내</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>20837</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20837</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>2026-07-02 13:16:19.799934+09:00</t>
         </is>

--- a/docs/snapshot/downloads/privacy.xlsx
+++ b/docs/snapshot/downloads/privacy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>개인정보 포털 예방점검에 따른 서비스 중단 안내 (8.13 19:00 ~ 23:00)</t>
+          <t>2026년 개인정보 영향평가 인증시험(2차) 안내</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,39 +476,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20909</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20915</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:01:43.365104+09:00</t>
+          <t>2026-09-03 14:16:40.776731+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:01:43.365104+09:00</t>
+          <t>2026-09-03 14:16:40.776731+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SKT  휴대폰 본인확인서비스 중단 공지(7.12 01:00 ~ 04:00)</t>
+          <t>개인정보 포털 예방점검에 따른 서비스 중단 안내 (8.13 19:00 ~ 23:00)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -518,39 +518,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20908</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20909</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-09 10:02:18.348370+09:00</t>
+          <t>2026-08-10 18:01:43.365104+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-09 10:02:18.348370+09:00</t>
+          <t>2026-08-10 18:01:43.365104+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 전문교육(하반기) 안내</t>
+          <t>SKT  휴대폰 본인확인서비스 중단 공지(7.12 01:00 ~ 04:00)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -560,39 +560,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20907</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20908</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
+          <t>2026-07-09 10:02:18.348370+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
+          <t>2026-07-09 10:02:18.348370+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인확인 내역조회, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.6.16 (화) 19:00 ~20:00)</t>
+          <t>2026년 개인정보 영향평가 전문교육(하반기) 안내</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20906</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20907</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -629,12 +629,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>정보주체 권리행사(본인확인 내역조회, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.6.16 (화) 19:00 ~20:00)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20903</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20906</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -671,12 +671,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>개인정보 포털 DB점검에 따른 서비스 중단 안내 (5.26 19:00 ~ 21:00)</t>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20900</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20903</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(복구완료) 외국인 실명확인 서비스 장애 안내(26.05.19 13:47 ~18:50 )</t>
+          <t>개인정보 포털 DB점검에 따른 서비스 중단 안내 (5.26 19:00 ~ 21:00)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20896</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20900</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제3기 가명정보 전문가 풀 모집 공고</t>
+          <t>(복구완료) 외국인 실명확인 서비스 장애 안내(26.05.19 13:47 ~18:50 )</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -770,17 +770,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20895</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20895</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20896</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -797,12 +797,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SKT 휴대폰 본인확인서비스 중단 공지(5.10 03:20 ~ 03:25 / 5.12 03:20 ~ 03:25)</t>
+          <t>제3기 가명정보 전문가 풀 모집 공고</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20894</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20895</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 인증시험(1차) 안내</t>
+          <t>SKT 휴대폰 본인확인서비스 중단 공지(5.10 03:20 ~ 03:25 / 5.12 03:20 ~ 03:25)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20893</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20894</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -881,12 +881,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>본인인증 서비스 장애 발생 공지(2026.04.28(화)15:00 ~ 15:10)</t>
+          <t>2026년 개인정보 영향평가 인증시험(1차) 안내</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20888</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20893</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -923,12 +923,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>개인정보 영향평가 전문인력 인증서 발급 및 유효기간 관련 안내</t>
+          <t>본인인증 서비스 장애 발생 공지(2026.04.28(화)15:00 ~ 15:10)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20884</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20888</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 계속교육 일정 안내</t>
+          <t>개인정보 영향평가 전문인력 인증서 발급 및 유효기간 관련 안내</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20878</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20884</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.4.8 (수) 03:00 ~05:00)</t>
+          <t>2026년 개인정보 영향평가 계속교육 일정 안내</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20875</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20878</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1049,12 +1049,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내 (2026년 3월 24일(화) 23:00~ 3월 25일(수) 02:00)</t>
+          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.4.8 (수) 03:00 ~05:00)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20874</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20875</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1091,12 +1091,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.03.24(화)22:00 ~ 2026.03.25(수) 02:00)</t>
+          <t>본인확인 서비스 작업 공지 안내 (2026년 3월 24일(화) 23:00~ 3월 25일(수) 02:00)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20873</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20874</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 전문교육(상반기) 안내</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.03.24(화)22:00 ~ 2026.03.25(수) 02:00)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20872</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20872</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20873</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>외국인 실명확인 서비스 작업 공지 안내</t>
+          <t>2026년 개인정보 영향평가 전문교육(상반기) 안내</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20871</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20872</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1217,12 +1217,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.03.24. (화) 02:00 ~ 04:00)</t>
+          <t>외국인 실명확인 서비스 작업 공지 안내</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20870</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20871</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.01.22 (목) 22:00 ~2026.01.23 (금) 05:00)</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.03.24. (화) 02:00 ~ 04:00)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20868</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20870</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1301,12 +1301,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.01.21 (수) 19:00 ~21:00)</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.01.22 (목) 22:00 ~2026.01.23 (금) 05:00)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20867</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20868</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1343,12 +1343,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>개인정보 포털 사용자 편의성 설문조사 참여 이벤트 당첨자 발표</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.01.21 (수) 19:00 ~21:00)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1358,17 +1358,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20866</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20867</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1385,12 +1385,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 보호·활용 분야 R&amp;amp;D 사업 신규지원 대상과제 공고(~2.10. 오후 3시)</t>
+          <t>개인정보 포털 사용자 편의성 설문조사 참여 이벤트 당첨자 발표</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1400,17 +1400,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20865</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20866</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1427,12 +1427,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.1.12 (월) 05:00 ~06:00)</t>
+          <t>2026년도 개인정보 보호·활용 분야 R&amp;amp;D 사업 신규지원 대상과제 공고(~2.10. 오후 3시)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20862</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20865</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1469,12 +1469,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>「개인정보관리 전문기관 지정 심사위원회」 심사위원 모집 안내 (~12.23. 18시까지)</t>
+          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.1.12 (월) 05:00 ~06:00)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20856</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20862</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>외국인 본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.17 (수) 16:00 ~17:00)</t>
+          <t>「개인정보관리 전문기관 지정 심사위원회」 심사위원 모집 안내 (~12.23. 18시까지)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1526,17 +1526,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20855</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20856</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.15 (월) 08:00 ~09:00)</t>
+          <t>외국인 본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.17 (수) 16:00 ~17:00)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20854</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20855</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1595,40 +1595,82 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.15 (월) 08:00 ~09:00)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>20854</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20854</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2025년 개인정보 영향평가 인증시험(2차) 안내</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>20837</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20837</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>2026-07-02 13:16:19.799934+09:00</t>
         </is>

--- a/docs/snapshot/downloads/privacy.xlsx
+++ b/docs/snapshot/downloads/privacy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 인증시험(2차) 안내</t>
+          <t>2026년 개인정보 보호주간(9.28.~10.2.) 포스터 및 앰블럼</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,39 +476,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20915</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20917</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:16:40.776731+09:00</t>
+          <t>2026-09-08 11:31:39.797854+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:16:40.776731+09:00</t>
+          <t>2026-09-08 11:31:39.797854+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>개인정보 포털 예방점검에 따른 서비스 중단 안내 (8.13 19:00 ~ 23:00)</t>
+          <t>2026년 개인정보 영향평가 인증시험(2차) 안내</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -518,39 +518,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20909</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20915</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-10 18:01:43.365104+09:00</t>
+          <t>2026-09-03 14:16:40.776731+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-10 18:01:43.365104+09:00</t>
+          <t>2026-09-03 14:16:40.776731+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKT  휴대폰 본인확인서비스 중단 공지(7.12 01:00 ~ 04:00)</t>
+          <t>개인정보 포털 예방점검에 따른 서비스 중단 안내 (8.13 19:00 ~ 23:00)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -560,39 +560,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20908</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20909</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-09 10:02:18.348370+09:00</t>
+          <t>2026-08-10 18:01:43.365104+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-09 10:02:18.348370+09:00</t>
+          <t>2026-08-10 18:01:43.365104+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 전문교육(하반기) 안내</t>
+          <t>SKT  휴대폰 본인확인서비스 중단 공지(7.12 01:00 ~ 04:00)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -602,39 +602,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20907</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20908</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
+          <t>2026-07-09 10:02:18.348370+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
+          <t>2026-07-09 10:02:18.348370+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인확인 내역조회, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.6.16 (화) 19:00 ~20:00)</t>
+          <t>2026년 개인정보 영향평가 전문교육(하반기) 안내</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20906</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20907</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -671,12 +671,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>정보주체 권리행사(본인확인 내역조회, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.6.16 (화) 19:00 ~20:00)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20903</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20906</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>개인정보 포털 DB점검에 따른 서비스 중단 안내 (5.26 19:00 ~ 21:00)</t>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20900</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20903</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(복구완료) 외국인 실명확인 서비스 장애 안내(26.05.19 13:47 ~18:50 )</t>
+          <t>개인정보 포털 DB점검에 따른 서비스 중단 안내 (5.26 19:00 ~ 21:00)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -770,17 +770,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20896</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20900</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -797,12 +797,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>제3기 가명정보 전문가 풀 모집 공고</t>
+          <t>(복구완료) 외국인 실명확인 서비스 장애 안내(26.05.19 13:47 ~18:50 )</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20895</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20895</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20896</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SKT 휴대폰 본인확인서비스 중단 공지(5.10 03:20 ~ 03:25 / 5.12 03:20 ~ 03:25)</t>
+          <t>제3기 가명정보 전문가 풀 모집 공고</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20894</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20895</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -881,12 +881,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 인증시험(1차) 안내</t>
+          <t>SKT 휴대폰 본인확인서비스 중단 공지(5.10 03:20 ~ 03:25 / 5.12 03:20 ~ 03:25)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20893</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20894</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -923,12 +923,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>본인인증 서비스 장애 발생 공지(2026.04.28(화)15:00 ~ 15:10)</t>
+          <t>2026년 개인정보 영향평가 인증시험(1차) 안내</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20888</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20893</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -965,12 +965,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>개인정보 영향평가 전문인력 인증서 발급 및 유효기간 관련 안내</t>
+          <t>본인인증 서비스 장애 발생 공지(2026.04.28(화)15:00 ~ 15:10)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20884</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20888</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 계속교육 일정 안내</t>
+          <t>개인정보 영향평가 전문인력 인증서 발급 및 유효기간 관련 안내</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20878</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20884</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1049,12 +1049,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.4.8 (수) 03:00 ~05:00)</t>
+          <t>2026년 개인정보 영향평가 계속교육 일정 안내</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20875</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20878</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1091,12 +1091,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내 (2026년 3월 24일(화) 23:00~ 3월 25일(수) 02:00)</t>
+          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.4.8 (수) 03:00 ~05:00)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1106,17 +1106,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20874</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20875</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.03.24(화)22:00 ~ 2026.03.25(수) 02:00)</t>
+          <t>본인확인 서비스 작업 공지 안내 (2026년 3월 24일(화) 23:00~ 3월 25일(수) 02:00)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20873</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20874</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 전문교육(상반기) 안내</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.03.24(화)22:00 ~ 2026.03.25(수) 02:00)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20872</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20872</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20873</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1217,12 +1217,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>외국인 실명확인 서비스 작업 공지 안내</t>
+          <t>2026년 개인정보 영향평가 전문교육(상반기) 안내</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20871</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20872</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.03.24. (화) 02:00 ~ 04:00)</t>
+          <t>외국인 실명확인 서비스 작업 공지 안내</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20870</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20871</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1301,12 +1301,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.01.22 (목) 22:00 ~2026.01.23 (금) 05:00)</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.03.24. (화) 02:00 ~ 04:00)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20868</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20870</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1343,12 +1343,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.01.21 (수) 19:00 ~21:00)</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.01.22 (목) 22:00 ~2026.01.23 (금) 05:00)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1358,17 +1358,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20867</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20868</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1385,12 +1385,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>개인정보 포털 사용자 편의성 설문조사 참여 이벤트 당첨자 발표</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.01.21 (수) 19:00 ~21:00)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1400,17 +1400,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20866</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20867</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1427,12 +1427,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 보호·활용 분야 R&amp;amp;D 사업 신규지원 대상과제 공고(~2.10. 오후 3시)</t>
+          <t>개인정보 포털 사용자 편의성 설문조사 참여 이벤트 당첨자 발표</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20865</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20866</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1469,12 +1469,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.1.12 (월) 05:00 ~06:00)</t>
+          <t>2026년도 개인정보 보호·활용 분야 R&amp;amp;D 사업 신규지원 대상과제 공고(~2.10. 오후 3시)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20862</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20865</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>「개인정보관리 전문기관 지정 심사위원회」 심사위원 모집 안내 (~12.23. 18시까지)</t>
+          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.1.12 (월) 05:00 ~06:00)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1526,17 +1526,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20856</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20862</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>외국인 본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.17 (수) 16:00 ~17:00)</t>
+          <t>「개인정보관리 전문기관 지정 심사위원회」 심사위원 모집 안내 (~12.23. 18시까지)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20855</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20856</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1595,12 +1595,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.15 (월) 08:00 ~09:00)</t>
+          <t>외국인 본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.17 (수) 16:00 ~17:00)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20854</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20855</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1637,40 +1637,82 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.15 (월) 08:00 ~09:00)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20854</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20854</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2025년 개인정보 영향평가 인증시험(2차) 안내</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>20837</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20837</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>2026-07-02 13:16:19.799934+09:00</t>
         </is>
